--- a/CDC WORK 2025 - 2026 dec.xlsx
+++ b/CDC WORK 2025 - 2026 dec.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TW - JFS" sheetId="13" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="328">
   <si>
     <t xml:space="preserve">DBMS TRAINING SCHEDULE IN CDC </t>
   </si>
@@ -1013,6 +1013,24 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Employee _JDBC ,student_jdbc through Maven</t>
+  </si>
+  <si>
+    <t>SB B3</t>
+  </si>
+  <si>
+    <t>Bootcamp</t>
+  </si>
+  <si>
+    <t>Virtusa Training</t>
+  </si>
+  <si>
+    <t>Hibernate OTM and MTO in Eclipse IDE</t>
+  </si>
+  <si>
+    <t>Holiday</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1068,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1180,6 +1198,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1353,7 +1377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1480,15 +1504,6 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1496,9 +1511,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1528,6 +1540,54 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1555,41 +1615,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3418,24 +3451,25 @@
     <col min="4" max="4" width="46.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.90625" customWidth="1"/>
     <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B2" s="49" t="s">
@@ -3603,20 +3637,20 @@
       <c r="B9" s="3">
         <v>45998</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="61"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="58"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="51" t="s">
@@ -3757,20 +3791,20 @@
       <c r="B16" s="3">
         <v>46005</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="61"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="58"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="51" t="s">
@@ -3913,20 +3947,20 @@
       <c r="B23" s="3">
         <v>46012</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="61"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="58"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
@@ -4001,20 +4035,20 @@
       <c r="B27" s="3">
         <v>46016</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="58"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="70"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="51" t="s">
@@ -4023,20 +4057,20 @@
       <c r="B28" s="3">
         <v>46017</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="68" t="s">
         <v>299</v>
       </c>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="58"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="51" t="s">
@@ -4067,20 +4101,20 @@
       <c r="B30" s="3">
         <v>46019</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="61"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="51" t="s">
@@ -4135,7 +4169,9 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4176,7 +4212,9 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -4196,7 +4234,9 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -4213,20 +4253,20 @@
       <c r="B37" s="3">
         <v>46026</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="60"/>
-      <c r="N37" s="61"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="51" t="s">
@@ -4238,7 +4278,9 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -4258,7 +4300,9 @@
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -4278,7 +4322,9 @@
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -4298,7 +4344,9 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -4318,7 +4366,9 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="F42" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -4338,7 +4388,9 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -4355,20 +4407,20 @@
       <c r="B44" s="3">
         <v>46033</v>
       </c>
-      <c r="C44" s="59" t="s">
+      <c r="C44" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="60"/>
-      <c r="E44" s="60"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="60"/>
-      <c r="I44" s="60"/>
-      <c r="J44" s="60"/>
-      <c r="K44" s="60"/>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="61"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="51" t="s">
@@ -4377,20 +4429,20 @@
       <c r="B45" s="3">
         <v>46034</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
-      <c r="I45" s="64"/>
-      <c r="J45" s="64"/>
-      <c r="K45" s="64"/>
-      <c r="L45" s="64"/>
-      <c r="M45" s="64"/>
-      <c r="N45" s="65"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="60"/>
+      <c r="L45" s="60"/>
+      <c r="M45" s="60"/>
+      <c r="N45" s="61"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="51" t="s">
@@ -4399,18 +4451,18 @@
       <c r="B46" s="3">
         <v>46035</v>
       </c>
-      <c r="C46" s="66"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="67"/>
-      <c r="J46" s="67"/>
-      <c r="K46" s="67"/>
-      <c r="L46" s="67"/>
-      <c r="M46" s="67"/>
-      <c r="N46" s="68"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="64"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="51" t="s">
@@ -4419,18 +4471,18 @@
       <c r="B47" s="3">
         <v>46036</v>
       </c>
-      <c r="C47" s="66"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="68"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="51" t="s">
@@ -4439,18 +4491,18 @@
       <c r="B48" s="3">
         <v>46037</v>
       </c>
-      <c r="C48" s="66"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67"/>
-      <c r="L48" s="67"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="68"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="64"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="51" t="s">
@@ -4459,18 +4511,18 @@
       <c r="B49" s="3">
         <v>46038</v>
       </c>
-      <c r="C49" s="66"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="67"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="68"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="63"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="63"/>
+      <c r="N49" s="64"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="51" t="s">
@@ -4479,18 +4531,18 @@
       <c r="B50" s="3">
         <v>46039</v>
       </c>
-      <c r="C50" s="69"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="70"/>
-      <c r="M50" s="70"/>
-      <c r="N50" s="71"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="66"/>
+      <c r="M50" s="66"/>
+      <c r="N50" s="67"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="51" t="s">
@@ -4499,20 +4551,20 @@
       <c r="B51" s="3">
         <v>46040</v>
       </c>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D51" s="60"/>
-      <c r="E51" s="60"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="60"/>
-      <c r="J51" s="60"/>
-      <c r="K51" s="60"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="60"/>
-      <c r="N51" s="61"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="51" t="s">
@@ -4524,7 +4576,9 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -4544,7 +4598,9 @@
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
+      <c r="F53" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -4564,7 +4620,9 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -4584,7 +4642,9 @@
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -4604,7 +4664,9 @@
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="F56" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -4624,7 +4686,9 @@
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="F57" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -4641,20 +4705,20 @@
       <c r="B58" s="3">
         <v>46047</v>
       </c>
-      <c r="C58" s="59" t="s">
+      <c r="C58" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="60"/>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="61"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="51" t="s">
@@ -4663,20 +4727,20 @@
       <c r="B59" s="3">
         <v>46048</v>
       </c>
-      <c r="C59" s="56" t="s">
+      <c r="C59" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
-      <c r="J59" s="57"/>
-      <c r="K59" s="57"/>
-      <c r="L59" s="57"/>
-      <c r="M59" s="57"/>
-      <c r="N59" s="58"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
+      <c r="L59" s="69"/>
+      <c r="M59" s="69"/>
+      <c r="N59" s="70"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="51" t="s">
@@ -4688,7 +4752,9 @@
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
+      <c r="F60" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -4881,20 +4947,20 @@
       <c r="B65" s="3">
         <v>46054</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D65" s="60"/>
-      <c r="E65" s="60"/>
-      <c r="F65" s="60"/>
-      <c r="G65" s="60"/>
-      <c r="H65" s="60"/>
-      <c r="I65" s="60"/>
-      <c r="J65" s="60"/>
-      <c r="K65" s="60"/>
-      <c r="L65" s="60"/>
-      <c r="M65" s="60"/>
-      <c r="N65" s="61"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
+      <c r="L65" s="57"/>
+      <c r="M65" s="57"/>
+      <c r="N65" s="58"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="51" t="s">
@@ -4950,7 +5016,9 @@
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4970,7 +5038,9 @@
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4990,7 +5060,9 @@
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="F69" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -5010,7 +5082,9 @@
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -5030,7 +5104,9 @@
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -5047,20 +5123,20 @@
       <c r="B72" s="3">
         <v>46061</v>
       </c>
-      <c r="C72" s="59" t="s">
+      <c r="C72" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="60"/>
-      <c r="E72" s="60"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="60"/>
-      <c r="H72" s="60"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="60"/>
-      <c r="K72" s="60"/>
-      <c r="L72" s="60"/>
-      <c r="M72" s="60"/>
-      <c r="N72" s="61"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
+      <c r="L72" s="57"/>
+      <c r="M72" s="57"/>
+      <c r="N72" s="58"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="51" t="s">
@@ -5072,8 +5148,12 @@
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
+      <c r="F73" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -5092,7 +5172,9 @@
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -5112,7 +5194,9 @@
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="F75" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -5132,7 +5216,9 @@
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="F76" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -5153,7 +5239,6 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
@@ -5169,18 +5254,20 @@
       <c r="B78" s="3">
         <v>46067</v>
       </c>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
+      <c r="C78" s="93" t="s">
+        <v>327</v>
+      </c>
+      <c r="D78" s="94"/>
+      <c r="E78" s="94"/>
+      <c r="F78" s="94"/>
+      <c r="G78" s="94"/>
+      <c r="H78" s="94"/>
+      <c r="I78" s="94"/>
+      <c r="J78" s="94"/>
+      <c r="K78" s="94"/>
+      <c r="L78" s="94"/>
+      <c r="M78" s="94"/>
+      <c r="N78" s="95"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="51" t="s">
@@ -5189,20 +5276,20 @@
       <c r="B79" s="3">
         <v>46068</v>
       </c>
-      <c r="C79" s="59" t="s">
+      <c r="C79" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="60"/>
-      <c r="K79" s="60"/>
-      <c r="L79" s="60"/>
-      <c r="M79" s="60"/>
-      <c r="N79" s="61"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="57"/>
+      <c r="L79" s="57"/>
+      <c r="M79" s="57"/>
+      <c r="N79" s="58"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="51" t="s">
@@ -5211,7 +5298,9 @@
       <c r="B80" s="3">
         <v>46069</v>
       </c>
-      <c r="C80" s="2"/>
+      <c r="C80" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
@@ -5331,20 +5420,20 @@
       <c r="B86" s="3">
         <v>46075</v>
       </c>
-      <c r="C86" s="59" t="s">
+      <c r="C86" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D86" s="60"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="60"/>
-      <c r="H86" s="60"/>
-      <c r="I86" s="60"/>
-      <c r="J86" s="60"/>
-      <c r="K86" s="60"/>
-      <c r="L86" s="60"/>
-      <c r="M86" s="60"/>
-      <c r="N86" s="61"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="57"/>
+      <c r="L86" s="57"/>
+      <c r="M86" s="57"/>
+      <c r="N86" s="58"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="51" t="s">
@@ -5473,20 +5562,20 @@
       <c r="B93" s="3">
         <v>46082</v>
       </c>
-      <c r="C93" s="59" t="s">
+      <c r="C93" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D93" s="60"/>
-      <c r="E93" s="60"/>
-      <c r="F93" s="60"/>
-      <c r="G93" s="60"/>
-      <c r="H93" s="60"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
-      <c r="K93" s="60"/>
-      <c r="L93" s="60"/>
-      <c r="M93" s="60"/>
-      <c r="N93" s="61"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
+      <c r="L93" s="57"/>
+      <c r="M93" s="57"/>
+      <c r="N93" s="58"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="51" t="s">
@@ -5515,20 +5604,20 @@
       <c r="B95" s="3">
         <v>46084</v>
       </c>
-      <c r="C95" s="56" t="s">
+      <c r="C95" s="68" t="s">
         <v>303</v>
       </c>
-      <c r="D95" s="57"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="57"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="57"/>
-      <c r="J95" s="57"/>
-      <c r="K95" s="57"/>
-      <c r="L95" s="57"/>
-      <c r="M95" s="57"/>
-      <c r="N95" s="58"/>
+      <c r="D95" s="69"/>
+      <c r="E95" s="69"/>
+      <c r="F95" s="69"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="69"/>
+      <c r="I95" s="69"/>
+      <c r="J95" s="69"/>
+      <c r="K95" s="69"/>
+      <c r="L95" s="69"/>
+      <c r="M95" s="69"/>
+      <c r="N95" s="70"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="51" t="s">
@@ -5617,20 +5706,20 @@
       <c r="B100" s="3">
         <v>46089</v>
       </c>
-      <c r="C100" s="59" t="s">
+      <c r="C100" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D100" s="60"/>
-      <c r="E100" s="60"/>
-      <c r="F100" s="60"/>
-      <c r="G100" s="60"/>
-      <c r="H100" s="60"/>
-      <c r="I100" s="60"/>
-      <c r="J100" s="60"/>
-      <c r="K100" s="60"/>
-      <c r="L100" s="60"/>
-      <c r="M100" s="60"/>
-      <c r="N100" s="61"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
+      <c r="L100" s="57"/>
+      <c r="M100" s="57"/>
+      <c r="N100" s="58"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="51" t="s">
@@ -5759,20 +5848,20 @@
       <c r="B107" s="3">
         <v>46096</v>
       </c>
-      <c r="C107" s="59" t="s">
+      <c r="C107" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D107" s="60"/>
-      <c r="E107" s="60"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="60"/>
-      <c r="H107" s="60"/>
-      <c r="I107" s="60"/>
-      <c r="J107" s="60"/>
-      <c r="K107" s="60"/>
-      <c r="L107" s="60"/>
-      <c r="M107" s="60"/>
-      <c r="N107" s="61"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
+      <c r="H107" s="57"/>
+      <c r="I107" s="57"/>
+      <c r="J107" s="57"/>
+      <c r="K107" s="57"/>
+      <c r="L107" s="57"/>
+      <c r="M107" s="57"/>
+      <c r="N107" s="58"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="51" t="s">
@@ -5841,20 +5930,20 @@
       <c r="B111" s="3">
         <v>46100</v>
       </c>
-      <c r="C111" s="56" t="s">
+      <c r="C111" s="68" t="s">
         <v>302</v>
       </c>
-      <c r="D111" s="57"/>
-      <c r="E111" s="57"/>
-      <c r="F111" s="57"/>
-      <c r="G111" s="57"/>
-      <c r="H111" s="57"/>
-      <c r="I111" s="57"/>
-      <c r="J111" s="57"/>
-      <c r="K111" s="57"/>
-      <c r="L111" s="57"/>
-      <c r="M111" s="57"/>
-      <c r="N111" s="58"/>
+      <c r="D111" s="69"/>
+      <c r="E111" s="69"/>
+      <c r="F111" s="69"/>
+      <c r="G111" s="69"/>
+      <c r="H111" s="69"/>
+      <c r="I111" s="69"/>
+      <c r="J111" s="69"/>
+      <c r="K111" s="69"/>
+      <c r="L111" s="69"/>
+      <c r="M111" s="69"/>
+      <c r="N111" s="70"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="51" t="s">
@@ -5883,20 +5972,20 @@
       <c r="B113" s="3">
         <v>46102</v>
       </c>
-      <c r="C113" s="56" t="s">
+      <c r="C113" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D113" s="57"/>
-      <c r="E113" s="57"/>
-      <c r="F113" s="57"/>
-      <c r="G113" s="57"/>
-      <c r="H113" s="57"/>
-      <c r="I113" s="57"/>
-      <c r="J113" s="57"/>
-      <c r="K113" s="57"/>
-      <c r="L113" s="57"/>
-      <c r="M113" s="57"/>
-      <c r="N113" s="58"/>
+      <c r="D113" s="69"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="69"/>
+      <c r="H113" s="69"/>
+      <c r="I113" s="69"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="69"/>
+      <c r="L113" s="69"/>
+      <c r="M113" s="69"/>
+      <c r="N113" s="70"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="51" t="s">
@@ -5905,20 +5994,20 @@
       <c r="B114" s="3">
         <v>46103</v>
       </c>
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D114" s="60"/>
-      <c r="E114" s="60"/>
-      <c r="F114" s="60"/>
-      <c r="G114" s="60"/>
-      <c r="H114" s="60"/>
-      <c r="I114" s="60"/>
-      <c r="J114" s="60"/>
-      <c r="K114" s="60"/>
-      <c r="L114" s="60"/>
-      <c r="M114" s="60"/>
-      <c r="N114" s="61"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="57"/>
+      <c r="J114" s="57"/>
+      <c r="K114" s="57"/>
+      <c r="L114" s="57"/>
+      <c r="M114" s="57"/>
+      <c r="N114" s="58"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="51" t="s">
@@ -6007,20 +6096,20 @@
       <c r="B119" s="3">
         <v>46108</v>
       </c>
-      <c r="C119" s="56" t="s">
+      <c r="C119" s="68" t="s">
         <v>300</v>
       </c>
-      <c r="D119" s="57"/>
-      <c r="E119" s="57"/>
-      <c r="F119" s="57"/>
-      <c r="G119" s="57"/>
-      <c r="H119" s="57"/>
-      <c r="I119" s="57"/>
-      <c r="J119" s="57"/>
-      <c r="K119" s="57"/>
-      <c r="L119" s="57"/>
-      <c r="M119" s="57"/>
-      <c r="N119" s="58"/>
+      <c r="D119" s="69"/>
+      <c r="E119" s="69"/>
+      <c r="F119" s="69"/>
+      <c r="G119" s="69"/>
+      <c r="H119" s="69"/>
+      <c r="I119" s="69"/>
+      <c r="J119" s="69"/>
+      <c r="K119" s="69"/>
+      <c r="L119" s="69"/>
+      <c r="M119" s="69"/>
+      <c r="N119" s="70"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="51" t="s">
@@ -6049,20 +6138,20 @@
       <c r="B121" s="3">
         <v>46110</v>
       </c>
-      <c r="C121" s="59" t="s">
+      <c r="C121" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="D121" s="60"/>
-      <c r="E121" s="60"/>
-      <c r="F121" s="60"/>
-      <c r="G121" s="60"/>
-      <c r="H121" s="60"/>
-      <c r="I121" s="60"/>
-      <c r="J121" s="60"/>
-      <c r="K121" s="60"/>
-      <c r="L121" s="60"/>
-      <c r="M121" s="60"/>
-      <c r="N121" s="61"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="57"/>
+      <c r="F121" s="57"/>
+      <c r="G121" s="57"/>
+      <c r="H121" s="57"/>
+      <c r="I121" s="57"/>
+      <c r="J121" s="57"/>
+      <c r="K121" s="57"/>
+      <c r="L121" s="57"/>
+      <c r="M121" s="57"/>
+      <c r="N121" s="58"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="51" t="s">
@@ -6085,7 +6174,18 @@
       <c r="N122" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
+    <mergeCell ref="C113:N113"/>
+    <mergeCell ref="C119:N119"/>
+    <mergeCell ref="C37:N37"/>
+    <mergeCell ref="C27:N27"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C9:N9"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C23:N23"/>
+    <mergeCell ref="C30:N30"/>
+    <mergeCell ref="C28:N28"/>
+    <mergeCell ref="C78:N78"/>
     <mergeCell ref="C121:N121"/>
     <mergeCell ref="C44:N44"/>
     <mergeCell ref="C51:N51"/>
@@ -6102,16 +6202,6 @@
     <mergeCell ref="C114:N114"/>
     <mergeCell ref="C95:N95"/>
     <mergeCell ref="C111:N111"/>
-    <mergeCell ref="C113:N113"/>
-    <mergeCell ref="C119:N119"/>
-    <mergeCell ref="C37:N37"/>
-    <mergeCell ref="C27:N27"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="C9:N9"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C30:N30"/>
-    <mergeCell ref="C28:N28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6119,14 +6209,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:E17"/>
+  <dimension ref="A3:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="8.7265625" style="1"/>
+    <col min="1" max="3" width="8.7265625" style="1"/>
     <col min="5" max="5" width="116.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="B3" s="1" t="s">
         <v>318</v>
       </c>
@@ -6134,7 +6227,10 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
@@ -6148,7 +6244,10 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
       <c r="B5" s="1">
         <v>5</v>
       </c>
@@ -6162,7 +6261,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -6176,7 +6278,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -6190,7 +6292,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>2</v>
       </c>
@@ -6204,13 +6306,13 @@
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D9" s="2" t="s">
         <v>257</v>
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D10" s="2" t="s">
         <v>259</v>
       </c>
@@ -6242,21 +6344,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B2" s="4" t="s">
@@ -6444,20 +6546,20 @@
       <c r="B9" s="3">
         <v>45851</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="61"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="58"/>
       <c r="R9" s="17"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.35">
@@ -6586,40 +6688,40 @@
       <c r="B16" s="3">
         <v>45858</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="61"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="58"/>
       <c r="R16" s="17"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B17" s="3">
         <v>45859</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="88"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="89"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
       <c r="R17" s="17"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.35">
@@ -6722,20 +6824,20 @@
       <c r="B23" s="3">
         <v>45865</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="61"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="58"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B24" s="3">
@@ -6857,20 +6959,20 @@
       <c r="B30" s="3">
         <v>45872</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="61"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B31" s="3">
@@ -6989,20 +7091,20 @@
       <c r="B37" s="3">
         <v>45879</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="60"/>
-      <c r="N37" s="61"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B38" s="3">
@@ -7082,58 +7184,58 @@
       <c r="B42" s="3">
         <v>45884</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="88"/>
-      <c r="E42" s="88"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="88"/>
-      <c r="H42" s="88"/>
-      <c r="I42" s="88"/>
-      <c r="J42" s="88"/>
-      <c r="K42" s="88"/>
-      <c r="L42" s="88"/>
-      <c r="M42" s="88"/>
-      <c r="N42" s="89"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="73"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B43" s="3">
         <v>45885</v>
       </c>
-      <c r="C43" s="87" t="s">
+      <c r="C43" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="88"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="88"/>
-      <c r="G43" s="88"/>
-      <c r="H43" s="88"/>
-      <c r="I43" s="88"/>
-      <c r="J43" s="88"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="88"/>
-      <c r="M43" s="88"/>
-      <c r="N43" s="89"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="73"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="73"/>
+      <c r="N43" s="74"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B44" s="3">
         <v>45886</v>
       </c>
-      <c r="C44" s="59" t="s">
+      <c r="C44" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="60"/>
-      <c r="E44" s="60"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="60"/>
-      <c r="I44" s="60"/>
-      <c r="J44" s="60"/>
-      <c r="K44" s="60"/>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="61"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B45" s="3">
@@ -7249,20 +7351,20 @@
       <c r="B51" s="3">
         <v>45893</v>
       </c>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="60"/>
-      <c r="E51" s="60"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="60"/>
-      <c r="J51" s="60"/>
-      <c r="K51" s="60"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="60"/>
-      <c r="N51" s="61"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B52" s="3">
@@ -7307,20 +7409,20 @@
       <c r="B54" s="3">
         <v>45896</v>
       </c>
-      <c r="C54" s="87" t="s">
+      <c r="C54" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="88"/>
-      <c r="L54" s="88"/>
-      <c r="M54" s="88"/>
-      <c r="N54" s="89"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B55" s="3">
@@ -7384,73 +7486,73 @@
       <c r="B58" s="3">
         <v>45900</v>
       </c>
-      <c r="C58" s="59" t="s">
+      <c r="C58" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="60"/>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="61"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B59" s="38">
         <v>45901</v>
       </c>
-      <c r="C59" s="72" t="s">
+      <c r="C59" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="73"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="73"/>
-      <c r="L59" s="73"/>
-      <c r="M59" s="73"/>
-      <c r="N59" s="74"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="85"/>
+      <c r="F59" s="85"/>
+      <c r="G59" s="85"/>
+      <c r="H59" s="85"/>
+      <c r="I59" s="85"/>
+      <c r="J59" s="85"/>
+      <c r="K59" s="85"/>
+      <c r="L59" s="85"/>
+      <c r="M59" s="85"/>
+      <c r="N59" s="86"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B60" s="38">
         <v>45902</v>
       </c>
-      <c r="C60" s="75"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="76"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="77"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="88"/>
+      <c r="E60" s="88"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="88"/>
+      <c r="H60" s="88"/>
+      <c r="I60" s="88"/>
+      <c r="J60" s="88"/>
+      <c r="K60" s="88"/>
+      <c r="L60" s="88"/>
+      <c r="M60" s="88"/>
+      <c r="N60" s="89"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B61" s="38">
         <v>45903</v>
       </c>
-      <c r="C61" s="78"/>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="80"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="91"/>
+      <c r="H61" s="91"/>
+      <c r="I61" s="91"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
+      <c r="L61" s="91"/>
+      <c r="M61" s="91"/>
+      <c r="N61" s="92"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B62" s="3">
@@ -7475,56 +7577,56 @@
       <c r="B63" s="3">
         <v>45905</v>
       </c>
-      <c r="C63" s="81" t="s">
+      <c r="C63" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="82"/>
-      <c r="H63" s="82"/>
-      <c r="I63" s="82"/>
-      <c r="J63" s="82"/>
-      <c r="K63" s="82"/>
-      <c r="L63" s="82"/>
-      <c r="M63" s="82"/>
-      <c r="N63" s="83"/>
+      <c r="D63" s="76"/>
+      <c r="E63" s="76"/>
+      <c r="F63" s="76"/>
+      <c r="G63" s="76"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="76"/>
+      <c r="J63" s="76"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="76"/>
+      <c r="M63" s="76"/>
+      <c r="N63" s="77"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B64" s="3">
         <v>45906</v>
       </c>
-      <c r="C64" s="84"/>
-      <c r="D64" s="85"/>
-      <c r="E64" s="85"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="85"/>
-      <c r="H64" s="85"/>
-      <c r="I64" s="85"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="85"/>
-      <c r="L64" s="85"/>
-      <c r="M64" s="85"/>
-      <c r="N64" s="86"/>
+      <c r="C64" s="81"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
+      <c r="H64" s="82"/>
+      <c r="I64" s="82"/>
+      <c r="J64" s="82"/>
+      <c r="K64" s="82"/>
+      <c r="L64" s="82"/>
+      <c r="M64" s="82"/>
+      <c r="N64" s="83"/>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B65" s="3">
         <v>45907</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="60"/>
-      <c r="E65" s="60"/>
-      <c r="F65" s="60"/>
-      <c r="G65" s="60"/>
-      <c r="H65" s="60"/>
-      <c r="I65" s="60"/>
-      <c r="J65" s="60"/>
-      <c r="K65" s="60"/>
-      <c r="L65" s="60"/>
-      <c r="M65" s="60"/>
-      <c r="N65" s="61"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
+      <c r="L65" s="57"/>
+      <c r="M65" s="57"/>
+      <c r="N65" s="58"/>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B66" s="3">
@@ -7643,20 +7745,20 @@
       <c r="B72" s="3">
         <v>45914</v>
       </c>
-      <c r="C72" s="59" t="s">
+      <c r="C72" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="60"/>
-      <c r="E72" s="60"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="60"/>
-      <c r="H72" s="60"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="60"/>
-      <c r="K72" s="60"/>
-      <c r="L72" s="60"/>
-      <c r="M72" s="60"/>
-      <c r="N72" s="61"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
+      <c r="L72" s="57"/>
+      <c r="M72" s="57"/>
+      <c r="N72" s="58"/>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B73" s="3">
@@ -7774,20 +7876,20 @@
       <c r="B79" s="3">
         <v>45921</v>
       </c>
-      <c r="C79" s="59" t="s">
+      <c r="C79" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="60"/>
-      <c r="K79" s="60"/>
-      <c r="L79" s="60"/>
-      <c r="M79" s="60"/>
-      <c r="N79" s="61"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="57"/>
+      <c r="L79" s="57"/>
+      <c r="M79" s="57"/>
+      <c r="N79" s="58"/>
     </row>
     <row r="80" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B80" s="3">
@@ -7903,143 +8005,143 @@
       <c r="B86" s="3">
         <v>45928</v>
       </c>
-      <c r="C86" s="59" t="s">
+      <c r="C86" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="60"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="60"/>
-      <c r="H86" s="60"/>
-      <c r="I86" s="60"/>
-      <c r="J86" s="60"/>
-      <c r="K86" s="60"/>
-      <c r="L86" s="60"/>
-      <c r="M86" s="60"/>
-      <c r="N86" s="61"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="57"/>
+      <c r="L86" s="57"/>
+      <c r="M86" s="57"/>
+      <c r="N86" s="58"/>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B87" s="3">
         <v>45929</v>
       </c>
-      <c r="C87" s="81" t="s">
+      <c r="C87" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="D87" s="82"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="82"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="83"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="76"/>
+      <c r="F87" s="76"/>
+      <c r="G87" s="76"/>
+      <c r="H87" s="76"/>
+      <c r="I87" s="76"/>
+      <c r="J87" s="76"/>
+      <c r="K87" s="76"/>
+      <c r="L87" s="76"/>
+      <c r="M87" s="76"/>
+      <c r="N87" s="77"/>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B88" s="3">
         <v>45930</v>
       </c>
-      <c r="C88" s="90"/>
-      <c r="D88" s="91"/>
-      <c r="E88" s="91"/>
-      <c r="F88" s="91"/>
-      <c r="G88" s="91"/>
-      <c r="H88" s="91"/>
-      <c r="I88" s="91"/>
-      <c r="J88" s="91"/>
-      <c r="K88" s="91"/>
-      <c r="L88" s="91"/>
-      <c r="M88" s="91"/>
-      <c r="N88" s="92"/>
+      <c r="C88" s="78"/>
+      <c r="D88" s="79"/>
+      <c r="E88" s="79"/>
+      <c r="F88" s="79"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="79"/>
+      <c r="I88" s="79"/>
+      <c r="J88" s="79"/>
+      <c r="K88" s="79"/>
+      <c r="L88" s="79"/>
+      <c r="M88" s="79"/>
+      <c r="N88" s="80"/>
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B89" s="3">
         <v>45931</v>
       </c>
-      <c r="C89" s="90"/>
-      <c r="D89" s="91"/>
-      <c r="E89" s="91"/>
-      <c r="F89" s="91"/>
-      <c r="G89" s="91"/>
-      <c r="H89" s="91"/>
-      <c r="I89" s="91"/>
-      <c r="J89" s="91"/>
-      <c r="K89" s="91"/>
-      <c r="L89" s="91"/>
-      <c r="M89" s="91"/>
-      <c r="N89" s="92"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
+      <c r="H89" s="79"/>
+      <c r="I89" s="79"/>
+      <c r="J89" s="79"/>
+      <c r="K89" s="79"/>
+      <c r="L89" s="79"/>
+      <c r="M89" s="79"/>
+      <c r="N89" s="80"/>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B90" s="3">
         <v>45932</v>
       </c>
-      <c r="C90" s="90"/>
-      <c r="D90" s="91"/>
-      <c r="E90" s="91"/>
-      <c r="F90" s="91"/>
-      <c r="G90" s="91"/>
-      <c r="H90" s="91"/>
-      <c r="I90" s="91"/>
-      <c r="J90" s="91"/>
-      <c r="K90" s="91"/>
-      <c r="L90" s="91"/>
-      <c r="M90" s="91"/>
-      <c r="N90" s="92"/>
+      <c r="C90" s="78"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="79"/>
+      <c r="F90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="79"/>
+      <c r="I90" s="79"/>
+      <c r="J90" s="79"/>
+      <c r="K90" s="79"/>
+      <c r="L90" s="79"/>
+      <c r="M90" s="79"/>
+      <c r="N90" s="80"/>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B91" s="3">
         <v>45933</v>
       </c>
-      <c r="C91" s="90"/>
-      <c r="D91" s="91"/>
-      <c r="E91" s="91"/>
-      <c r="F91" s="91"/>
-      <c r="G91" s="91"/>
-      <c r="H91" s="91"/>
-      <c r="I91" s="91"/>
-      <c r="J91" s="91"/>
-      <c r="K91" s="91"/>
-      <c r="L91" s="91"/>
-      <c r="M91" s="91"/>
-      <c r="N91" s="92"/>
+      <c r="C91" s="78"/>
+      <c r="D91" s="79"/>
+      <c r="E91" s="79"/>
+      <c r="F91" s="79"/>
+      <c r="G91" s="79"/>
+      <c r="H91" s="79"/>
+      <c r="I91" s="79"/>
+      <c r="J91" s="79"/>
+      <c r="K91" s="79"/>
+      <c r="L91" s="79"/>
+      <c r="M91" s="79"/>
+      <c r="N91" s="80"/>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B92" s="3">
         <v>45934</v>
       </c>
-      <c r="C92" s="84"/>
-      <c r="D92" s="85"/>
-      <c r="E92" s="85"/>
-      <c r="F92" s="85"/>
-      <c r="G92" s="85"/>
-      <c r="H92" s="85"/>
-      <c r="I92" s="85"/>
-      <c r="J92" s="85"/>
-      <c r="K92" s="85"/>
-      <c r="L92" s="85"/>
-      <c r="M92" s="85"/>
-      <c r="N92" s="86"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="82"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="82"/>
+      <c r="I92" s="82"/>
+      <c r="J92" s="82"/>
+      <c r="K92" s="82"/>
+      <c r="L92" s="82"/>
+      <c r="M92" s="82"/>
+      <c r="N92" s="83"/>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B93" s="3">
         <v>45935</v>
       </c>
-      <c r="C93" s="59" t="s">
+      <c r="C93" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="60"/>
-      <c r="E93" s="60"/>
-      <c r="F93" s="60"/>
-      <c r="G93" s="60"/>
-      <c r="H93" s="60"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
-      <c r="K93" s="60"/>
-      <c r="L93" s="60"/>
-      <c r="M93" s="60"/>
-      <c r="N93" s="61"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
+      <c r="L93" s="57"/>
+      <c r="M93" s="57"/>
+      <c r="N93" s="58"/>
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B94" s="3">
@@ -8155,20 +8257,20 @@
       <c r="B100" s="3">
         <v>45942</v>
       </c>
-      <c r="C100" s="59" t="s">
+      <c r="C100" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="60"/>
-      <c r="E100" s="60"/>
-      <c r="F100" s="60"/>
-      <c r="G100" s="60"/>
-      <c r="H100" s="60"/>
-      <c r="I100" s="60"/>
-      <c r="J100" s="60"/>
-      <c r="K100" s="60"/>
-      <c r="L100" s="60"/>
-      <c r="M100" s="60"/>
-      <c r="N100" s="61"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
+      <c r="L100" s="57"/>
+      <c r="M100" s="57"/>
+      <c r="N100" s="58"/>
     </row>
     <row r="101" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B101" s="3">
@@ -8267,58 +8369,58 @@
       <c r="B106" s="3">
         <v>45948</v>
       </c>
-      <c r="C106" s="87" t="s">
+      <c r="C106" s="72" t="s">
         <v>196</v>
       </c>
-      <c r="D106" s="88"/>
-      <c r="E106" s="88"/>
-      <c r="F106" s="88"/>
-      <c r="G106" s="88"/>
-      <c r="H106" s="88"/>
-      <c r="I106" s="88"/>
-      <c r="J106" s="88"/>
-      <c r="K106" s="88"/>
-      <c r="L106" s="88"/>
-      <c r="M106" s="88"/>
-      <c r="N106" s="89"/>
+      <c r="D106" s="73"/>
+      <c r="E106" s="73"/>
+      <c r="F106" s="73"/>
+      <c r="G106" s="73"/>
+      <c r="H106" s="73"/>
+      <c r="I106" s="73"/>
+      <c r="J106" s="73"/>
+      <c r="K106" s="73"/>
+      <c r="L106" s="73"/>
+      <c r="M106" s="73"/>
+      <c r="N106" s="74"/>
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B107" s="3">
         <v>45949</v>
       </c>
-      <c r="C107" s="59" t="s">
+      <c r="C107" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="60"/>
-      <c r="E107" s="60"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="60"/>
-      <c r="H107" s="60"/>
-      <c r="I107" s="60"/>
-      <c r="J107" s="60"/>
-      <c r="K107" s="60"/>
-      <c r="L107" s="60"/>
-      <c r="M107" s="60"/>
-      <c r="N107" s="61"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
+      <c r="H107" s="57"/>
+      <c r="I107" s="57"/>
+      <c r="J107" s="57"/>
+      <c r="K107" s="57"/>
+      <c r="L107" s="57"/>
+      <c r="M107" s="57"/>
+      <c r="N107" s="58"/>
     </row>
     <row r="108" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B108" s="3">
         <v>45950</v>
       </c>
-      <c r="C108" s="87" t="s">
+      <c r="C108" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="88"/>
-      <c r="E108" s="88"/>
-      <c r="F108" s="88"/>
-      <c r="G108" s="88"/>
-      <c r="H108" s="88"/>
-      <c r="I108" s="88"/>
-      <c r="J108" s="88"/>
-      <c r="K108" s="88"/>
-      <c r="L108" s="88"/>
-      <c r="M108" s="88"/>
-      <c r="N108" s="89"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="73"/>
+      <c r="F108" s="73"/>
+      <c r="G108" s="73"/>
+      <c r="H108" s="73"/>
+      <c r="I108" s="73"/>
+      <c r="J108" s="73"/>
+      <c r="K108" s="73"/>
+      <c r="L108" s="73"/>
+      <c r="M108" s="73"/>
+      <c r="N108" s="74"/>
     </row>
     <row r="109" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B109" s="3">
@@ -8417,20 +8519,20 @@
       <c r="B114" s="3">
         <v>45956</v>
       </c>
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="60"/>
-      <c r="E114" s="60"/>
-      <c r="F114" s="60"/>
-      <c r="G114" s="60"/>
-      <c r="H114" s="60"/>
-      <c r="I114" s="60"/>
-      <c r="J114" s="60"/>
-      <c r="K114" s="60"/>
-      <c r="L114" s="60"/>
-      <c r="M114" s="60"/>
-      <c r="N114" s="61"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="57"/>
+      <c r="J114" s="57"/>
+      <c r="K114" s="57"/>
+      <c r="L114" s="57"/>
+      <c r="M114" s="57"/>
+      <c r="N114" s="58"/>
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B115" s="3">
@@ -8549,20 +8651,20 @@
       <c r="B121" s="3">
         <v>45963</v>
       </c>
-      <c r="C121" s="59" t="s">
+      <c r="C121" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="60"/>
-      <c r="E121" s="60"/>
-      <c r="F121" s="60"/>
-      <c r="G121" s="60"/>
-      <c r="H121" s="60"/>
-      <c r="I121" s="60"/>
-      <c r="J121" s="60"/>
-      <c r="K121" s="60"/>
-      <c r="L121" s="60"/>
-      <c r="M121" s="60"/>
-      <c r="N121" s="61"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="57"/>
+      <c r="F121" s="57"/>
+      <c r="G121" s="57"/>
+      <c r="H121" s="57"/>
+      <c r="I121" s="57"/>
+      <c r="J121" s="57"/>
+      <c r="K121" s="57"/>
+      <c r="L121" s="57"/>
+      <c r="M121" s="57"/>
+      <c r="N121" s="58"/>
       <c r="O121" t="s">
         <v>199</v>
       </c>
@@ -8613,20 +8715,20 @@
       <c r="B124" s="3">
         <v>45966</v>
       </c>
-      <c r="C124" s="87" t="s">
+      <c r="C124" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="D124" s="88"/>
-      <c r="E124" s="88"/>
-      <c r="F124" s="88"/>
-      <c r="G124" s="88"/>
-      <c r="H124" s="88"/>
-      <c r="I124" s="88"/>
-      <c r="J124" s="88"/>
-      <c r="K124" s="88"/>
-      <c r="L124" s="88"/>
-      <c r="M124" s="88"/>
-      <c r="N124" s="89"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="73"/>
+      <c r="J124" s="73"/>
+      <c r="K124" s="73"/>
+      <c r="L124" s="73"/>
+      <c r="M124" s="73"/>
+      <c r="N124" s="74"/>
       <c r="O124" t="s">
         <v>199</v>
       </c>
@@ -8879,6 +8981,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C58:N58"/>
+    <mergeCell ref="C59:N61"/>
+    <mergeCell ref="C63:N64"/>
+    <mergeCell ref="C37:N37"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C42:N42"/>
+    <mergeCell ref="C43:N43"/>
+    <mergeCell ref="C54:N54"/>
+    <mergeCell ref="C44:N44"/>
+    <mergeCell ref="C51:N51"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C9:N9"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C23:N23"/>
+    <mergeCell ref="C30:N30"/>
     <mergeCell ref="C65:N65"/>
     <mergeCell ref="C108:N108"/>
     <mergeCell ref="C124:N124"/>
@@ -8892,21 +9009,6 @@
     <mergeCell ref="C72:N72"/>
     <mergeCell ref="C79:N79"/>
     <mergeCell ref="C106:N106"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="C9:N9"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C30:N30"/>
-    <mergeCell ref="C58:N58"/>
-    <mergeCell ref="C59:N61"/>
-    <mergeCell ref="C63:N64"/>
-    <mergeCell ref="C37:N37"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="C43:N43"/>
-    <mergeCell ref="C54:N54"/>
-    <mergeCell ref="C44:N44"/>
-    <mergeCell ref="C51:N51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
